--- a/data/trans_bre/P1805_2016_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1805_2016_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,78</t>
+          <t>0,47; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,18</t>
+          <t>-1,26; 2,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 291,26</t>
+          <t>12,22; 286,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 138,16</t>
+          <t>-33,41; 135,0</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,07</t>
+          <t>0,95; 3,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,85</t>
+          <t>-0,63; 1,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,39; 234,91</t>
+          <t>40,37; 215,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 80,05</t>
+          <t>-14,86; 78,55</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,1</t>
+          <t>-0,44; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,77</t>
+          <t>-0,38; 4,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 414,07</t>
+          <t>-29,87; 378,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 173,43</t>
+          <t>-13,2; 159,55</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,76</t>
+          <t>1,15; 2,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,78</t>
+          <t>-0,02; 1,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,73; 188,33</t>
+          <t>52,59; 189,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 67,87</t>
+          <t>-1,3; 66,6</t>
         </is>
       </c>
     </row>
